--- a/verification/cases/roundtrip/autofilter/init.xlsx
+++ b/verification/cases/roundtrip/autofilter/init.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" autoCompressPictures="0"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{762696E8-084E-4686-B121-6DB1CED5F96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="0" windowWidth="25360" windowHeight="18780" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="No Filter" sheetId="1" r:id="rId1"/>
@@ -172,7 +173,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -246,6 +247,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -570,11 +579,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -591,7 +600,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -608,7 +617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -625,7 +634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -642,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -659,7 +668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -676,7 +685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -690,7 +699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -704,7 +713,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -718,7 +727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -732,7 +741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -743,7 +752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -757,7 +766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -768,7 +777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -779,7 +788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -790,7 +799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -804,7 +813,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -818,7 +827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -832,7 +841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -846,7 +855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -860,7 +869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -871,7 +880,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -894,12 +903,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -916,7 +925,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -933,7 +942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -950,7 +959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -967,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -984,7 +993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1001,7 +1010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1016,7 +1025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1031,7 +1040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -1046,7 +1055,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -1061,7 +1070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -1074,7 +1083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1089,7 +1098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1102,7 +1111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1115,7 +1124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1128,7 +1137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1143,7 +1152,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -1158,7 +1167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -1173,7 +1182,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1188,7 +1197,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1203,7 +1212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -1216,7 +1225,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -1230,7 +1239,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000009000000}">
     <filterColumn colId="0">
       <customFilters and="1">
         <customFilter operator="greaterThanOrEqual" val="2"/>
@@ -1248,12 +1257,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1270,7 +1279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -1287,7 +1296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -1304,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -1321,7 +1330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -1338,7 +1347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -1355,7 +1364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -1370,7 +1379,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -1385,7 +1394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -1400,7 +1409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -1415,7 +1424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -1428,7 +1437,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -1443,7 +1452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -1456,7 +1465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -1469,7 +1478,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -1482,7 +1491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -1497,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -1512,7 +1521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -1527,7 +1536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -1542,7 +1551,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -1557,7 +1566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -1570,7 +1579,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -1584,7 +1593,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-00000A000000}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="greaterThanOrEqual" val="4"/>
@@ -1602,11 +1611,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1623,7 +1632,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1640,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -1657,7 +1666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -1674,7 +1683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -1691,7 +1700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1708,7 +1717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -1722,7 +1731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1736,7 +1745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1750,7 +1759,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1764,7 +1773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -1775,7 +1784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -1789,7 +1798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -1800,7 +1809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -1811,7 +1820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -1836,7 +1845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1850,7 +1859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -1864,7 +1873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -1878,7 +1887,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1892,7 +1901,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -1903,7 +1912,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -1915,7 +1924,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22"/>
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" verticalDpi="4294967292"/>
   <extLst>
@@ -1927,12 +1936,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1949,7 +1958,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>5</v>
       </c>
@@ -1966,7 +1975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -1983,7 +1992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>5</v>
       </c>
@@ -2000,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
@@ -2017,7 +2026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -2034,7 +2043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -2048,7 +2057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
@@ -2062,7 +2071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3</v>
       </c>
@@ -2076,7 +2085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2</v>
       </c>
@@ -2090,7 +2099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>2</v>
       </c>
@@ -2101,7 +2110,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2</v>
       </c>
@@ -2115,7 +2124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1</v>
       </c>
@@ -2126,7 +2135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1</v>
       </c>
@@ -2137,7 +2146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1</v>
       </c>
@@ -2148,7 +2157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1</v>
       </c>
@@ -2162,7 +2171,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1</v>
       </c>
@@ -2176,7 +2185,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1</v>
       </c>
@@ -2190,7 +2199,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1</v>
       </c>
@@ -2204,7 +2213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1</v>
       </c>
@@ -2218,7 +2227,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1</v>
       </c>
@@ -2229,7 +2238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>2</v>
       </c>
@@ -2241,7 +2250,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="1"/>
@@ -2258,12 +2267,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2280,7 +2289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -2297,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -2314,7 +2323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -2331,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -2348,7 +2357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2365,7 +2374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2380,7 +2389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -2395,7 +2404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -2410,7 +2419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -2425,7 +2434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -2438,7 +2447,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -2453,7 +2462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -2466,7 +2475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -2479,7 +2488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -2492,7 +2501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -2507,7 +2516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -2522,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -2537,7 +2546,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -2552,7 +2561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2567,7 +2576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -2580,7 +2589,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -2594,7 +2603,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="1"/>
@@ -2616,12 +2625,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2638,7 +2647,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -2655,7 +2664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -2672,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -2689,7 +2698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -2706,7 +2715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -2723,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -2738,7 +2747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -2753,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -2768,7 +2777,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -2783,7 +2792,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -2796,7 +2805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -2811,7 +2820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -2824,7 +2833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -2837,7 +2846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -2850,7 +2859,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -2865,7 +2874,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -2880,7 +2889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -2895,7 +2904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -2910,7 +2919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -2925,7 +2934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -2938,7 +2947,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -2952,7 +2961,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <filterColumn colId="0">
       <top10 val="10" filterVal="2"/>
     </filterColumn>
@@ -2967,12 +2976,12 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2989,7 +2998,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -3006,7 +3015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -3023,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -3040,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -3057,7 +3066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3074,7 +3083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3089,7 +3098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -3104,7 +3113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -3119,7 +3128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3134,7 +3143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3147,7 +3156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3162,7 +3171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -3175,7 +3184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -3188,7 +3197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -3201,7 +3210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -3216,7 +3225,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -3231,7 +3240,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -3246,7 +3255,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -3261,7 +3270,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -3276,7 +3285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -3289,7 +3298,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -3303,7 +3312,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000005000000}">
     <filterColumn colId="0">
       <top10 top="0" val="10" filterVal="2"/>
     </filterColumn>
@@ -3318,12 +3327,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3340,7 +3349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -3357,7 +3366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -3374,7 +3383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -3391,7 +3400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -3408,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3425,7 +3434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3440,7 +3449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -3455,7 +3464,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -3470,7 +3479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3485,7 +3494,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3498,7 +3507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3513,7 +3522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -3526,7 +3535,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -3539,7 +3548,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -3552,7 +3561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -3567,7 +3576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -3582,7 +3591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -3597,7 +3606,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -3612,7 +3621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -3627,7 +3636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -3640,7 +3649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -3654,7 +3663,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000006000000}">
     <filterColumn colId="0">
       <dynamicFilter type="belowAverage" val="2.3809523809523809"/>
     </filterColumn>
@@ -3672,12 +3681,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3694,7 +3703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -3711,7 +3720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -3728,7 +3737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -3745,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -3762,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -3779,7 +3788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -3794,7 +3803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -3809,7 +3818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1">
+    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -3824,7 +3833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3839,7 +3848,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3852,7 +3861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3867,7 +3876,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -3880,7 +3889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -3893,7 +3902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -3906,7 +3915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -3921,7 +3930,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -3936,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -3951,7 +3960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -3966,7 +3975,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -3981,7 +3990,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -3994,7 +4003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -4008,7 +4017,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000007000000}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="notEqual" val="3"/>
@@ -4025,12 +4034,12 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr filterMode="1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4047,7 +4056,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>5</v>
       </c>
@@ -4064,7 +4073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>5</v>
       </c>
@@ -4081,7 +4090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>5</v>
       </c>
@@ -4098,7 +4107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>5</v>
       </c>
@@ -4115,7 +4124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -4132,7 +4141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>3</v>
       </c>
@@ -4147,7 +4156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3</v>
       </c>
@@ -4162,7 +4171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -4177,7 +4186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -4192,7 +4201,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -4205,7 +4214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -4220,7 +4229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -4233,7 +4242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1</v>
       </c>
@@ -4246,7 +4255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1</v>
       </c>
@@ -4259,7 +4268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1</v>
       </c>
@@ -4274,7 +4283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -4289,7 +4298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1</v>
       </c>
@@ -4304,7 +4313,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1</v>
       </c>
@@ -4319,7 +4328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1</v>
       </c>
@@ -4334,7 +4343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1</v>
       </c>
@@ -4347,7 +4356,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -4361,7 +4370,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E22">
+  <autoFilter ref="A1:E22" xr:uid="{00000000-0009-0000-0000-000008000000}">
     <filterColumn colId="0">
       <customFilters>
         <customFilter operator="greaterThan" val="2"/>
